--- a/06_Test_Execution/BharatBites_Test_Execution.xlsx
+++ b/06_Test_Execution/BharatBites_Test_Execution.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Execution" sheetId="1" r:id="R1fecd26e00cf4534"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Execution" sheetId="1" r:id="R765f36b476e8450c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -523,7 +523,7 @@
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>Observed behavior matched the expected result: Relevant results display.</x:v>
+        <x:v>Food and restaurant searches returned relevant results matching the submitted search terms.</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
         <x:v>Pass</x:v>
@@ -1872,7 +1872,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbce79dbd44954956"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0484f1765cdf452e"/>
   </x:tableParts>
 </x:worksheet>
 </file>